--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -12425,17 +12425,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12457,17 +12457,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12617,17 +12617,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12841,17 +12841,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -13097,17 +13097,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13193,17 +13193,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13289,17 +13289,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13508,22 +13508,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12393,17 +12393,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -12425,17 +12425,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -12553,17 +12553,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12617,17 +12617,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12905,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13001,17 +13001,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13193,17 +13193,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13252,22 +13252,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
@@ -13289,17 +13289,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,22 +13444,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13577,17 +13577,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13636,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12617,17 +12617,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -12777,17 +12777,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12836,22 +12836,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12905,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13033,17 +13033,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13161,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,7 +13444,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13508,22 +13508,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13636,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,14 +12573,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -12590,12 +12590,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12772,22 +12772,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12809,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,29 +12861,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,14 +12893,14 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13321,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,22 +13444,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13636,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12457,17 +12457,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12553,17 +12553,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12649,17 +12649,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12809,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,29 +12861,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13129,17 +13129,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13225,17 +13225,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -13257,17 +13257,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -13289,17 +13289,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13321,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -13444,22 +13444,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13636,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12393,17 +12393,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -12553,17 +12553,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12649,17 +12649,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,29 +12861,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12905,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12925,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -13225,17 +13225,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -13289,17 +13289,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13321,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,7 +13444,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13545,17 +13545,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13604,22 +13604,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12393,17 +12393,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12457,17 +12457,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,14 +12829,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12905,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12925,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13001,17 +13001,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -13033,17 +13033,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13161,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13289,17 +13289,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -13412,22 +13412,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13449,17 +13449,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13508,7 +13508,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13545,17 +13545,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13646,12 +13646,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -12393,17 +12393,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12750,12 +12750,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13124,22 +13124,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13449,17 +13449,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13508,7 +13508,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13577,17 +13577,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13604,22 +13604,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -12617,17 +12617,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12772,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13124,22 +13124,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -13193,17 +13193,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13321,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,29 +13405,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,7 +13540,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
@@ -12617,17 +12617,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -12745,17 +12745,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13001,17 +13001,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13033,17 +13033,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13321,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13412,22 +13412,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,22 +13444,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13481,17 +13481,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13508,22 +13508,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,7 +13540,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12425,17 +12425,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12484,22 +12484,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12809,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12942,12 +12942,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13001,17 +13001,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13097,17 +13097,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13161,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,14 +13213,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -13230,12 +13230,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13289,17 +13289,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13481,17 +13481,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13545,17 +13545,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13577,17 +13577,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,14 +12765,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12809,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12925,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13161,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -13257,17 +13257,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,22 +13444,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12430,12 +12430,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12521,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -12649,17 +12649,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -12745,17 +12745,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12777,17 +12777,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12841,17 +12841,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12925,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,14 +12989,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13033,17 +13033,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -13193,17 +13193,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -13225,17 +13225,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13412,22 +13412,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13449,17 +13449,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13577,17 +13577,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12425,17 +12425,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,14 +12509,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12676,22 +12676,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12777,17 +12777,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,29 +12861,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12905,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12964,22 +12964,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,29 +13053,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13161,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -13193,17 +13193,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
@@ -13225,17 +13225,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,29 +13405,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,22 +13444,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13476,22 +13476,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13636,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,14 +12413,14 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,29 +12477,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12526,12 +12526,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12580,22 +12580,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12617,17 +12617,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,14 +12829,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12873,17 +12873,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12925,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13161,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13225,17 +13225,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,29 +13405,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13444,7 +13444,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13481,17 +13481,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13572,22 +13572,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12393,17 +12393,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12457,17 +12457,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -12553,17 +12553,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12669,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12701,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12733,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12765,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,29 +12797,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,14 +12829,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,29 +12861,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12893,29 +12893,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12925,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12969,17 +12969,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13001,17 +13001,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -13097,17 +13097,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13277,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13309,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -13449,17 +13449,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13508,22 +13508,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13604,22 +13604,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13636,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12388,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12413,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,29 +12445,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12489,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12573,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12605,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12637,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12681,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
@@ -12772,22 +12772,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12809,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12829,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12900,22 +12900,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12937,17 +12937,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,29 +12989,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13021,29 +13021,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,29 +13085,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13117,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13149,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,29 +13181,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,29 +13213,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,29 +13245,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13316,22 +13316,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13353,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13385,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13417,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13449,17 +13449,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13508,22 +13508,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13540,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13577,17 +13577,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13641,17 +13641,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8791</v>
+        <v>8793</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8774</v>
+        <v>8776</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-17</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="2" t="n">
@@ -6626,66 +6626,66 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>-1</v>
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D274" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E274" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D275" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E275" s="2" t="n">
-        <v>0</v>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="276">
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>0</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,59 +7179,59 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D299" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C301" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D299" s="2" t="n">
+      <c r="D301" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E299" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D300" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E300" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="D301" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="E301" s="4" t="n">
-        <v>1</v>
+      <c r="E301" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7242,14 +7242,14 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C302" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E302" s="4" t="n">
         <v>1</v>
@@ -7263,59 +7263,59 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="C303" s="4" t="n">
+      <c r="C305" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="D303" s="4" t="n">
+      <c r="D305" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E303" s="4" t="n">
+      <c r="E305" s="4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D304" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E304" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D305" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E305" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>0</v>
@@ -7914,59 +7914,59 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
+      <c r="C336" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D334" s="2" t="n">
+      <c r="D336" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E334" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C335" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D335" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="E335" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="D336" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>-1</v>
+      <c r="E336" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -7977,59 +7977,59 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C337" s="3" t="n">
+      <c r="C339" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="D337" s="3" t="n">
+      <c r="D339" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E337" s="3" t="n">
+      <c r="E339" s="3" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C338" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D338" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E338" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C339" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D339" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E339" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
@@ -8523,14 +8523,14 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D364" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E364" s="2" t="n">
         <v>0</v>
@@ -8560,19 +8560,19 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E365" s="2" t="n">
         <v>0</v>
@@ -8581,19 +8581,19 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C366" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E366" s="2" t="n">
         <v>0</v>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
@@ -8691,14 +8691,14 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E373" s="2" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -8791,19 +8791,19 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D400" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E400" s="2" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D403" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E403" s="2" t="n">
         <v>0</v>
@@ -9384,59 +9384,59 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C404" s="2" t="n">
+      <c r="C406" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D404" s="2" t="n">
+      <c r="D406" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E404" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="3" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C405" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="D405" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="E405" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B406" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C406" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="D406" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="E406" s="3" t="n">
-        <v>-2</v>
+      <c r="E406" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C407" s="3" t="n">
-        <v>206</v>
+        <v>107</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="E407" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="408">
@@ -9468,17 +9468,17 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E408" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="409">
@@ -9489,59 +9489,59 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="E409" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="inlineStr">
+      <c r="A410" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C410" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="D410" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="E410" s="2" t="n">
-        <v>0</v>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="inlineStr">
+      <c r="A411" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B411" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C411" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D411" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E411" s="2" t="n">
-        <v>0</v>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C411" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E411" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="412">
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,59 +9804,59 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C424" s="2" t="n">
+      <c r="C426" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D424" s="2" t="n">
+      <c r="D426" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E424" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B425" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C425" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="D425" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="E425" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B426" s="4" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C426" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D426" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="E426" s="4" t="n">
-        <v>1</v>
+      <c r="E426" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C427" s="4" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E427" s="4" t="n">
         <v>1</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C428" s="4" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E428" s="4" t="n">
         <v>1</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C429" s="4" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>1</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,17 +9972,17 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E432" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9993,17 +9993,17 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E433" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="E434" s="4" t="n">
         <v>2</v>
@@ -10035,16 +10035,58 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C436" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="D436" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="E436" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B437" s="4" t="inlineStr">
+        <is>
           <t>河北</t>
         </is>
       </c>
-      <c r="C435" s="4" t="n">
+      <c r="C437" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="D435" s="4" t="n">
+      <c r="D437" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E435" s="4" t="n">
+      <c r="E437" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10374,7 +10416,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10389,7 +10431,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10443,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10416,7 +10458,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10686,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10779,7 +10821,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10794,7 +10836,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10848,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10821,7 +10863,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11301,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11274,7 +11316,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11328,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11301,7 +11343,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11382,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11355,7 +11397,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11409,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11382,7 +11424,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11463,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11436,7 +11478,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11490,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11463,7 +11505,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11517,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11490,7 +11532,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11679,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11652,7 +11694,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11706,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11679,7 +11721,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12430,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12413,29 +12455,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12445,7 +12487,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
@@ -12457,17 +12499,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12477,7 +12519,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12531,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12509,29 +12551,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12541,7 +12583,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12553,17 +12595,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12573,29 +12615,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12605,29 +12647,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12637,29 +12679,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12669,29 +12711,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12701,29 +12743,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12733,29 +12775,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12765,29 +12807,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12797,7 +12839,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12851,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12829,29 +12871,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12861,7 +12903,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -12900,22 +12942,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12925,29 +12967,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12957,29 +12999,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12989,7 +13031,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -13033,17 +13075,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13053,7 +13095,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13107,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13085,7 +13127,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -13097,17 +13139,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13117,29 +13159,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13149,29 +13191,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13181,14 +13223,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -13198,12 +13240,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13213,7 +13255,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -13225,17 +13267,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13245,14 +13287,14 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13262,12 +13304,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13277,29 +13319,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13309,29 +13351,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13341,7 +13383,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13395,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13373,7 +13415,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13385,17 +13427,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13405,7 +13447,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13417,17 +13459,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13454,12 +13496,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13481,17 +13523,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13508,22 +13550,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13540,22 +13582,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13604,22 +13646,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13636,22 +13678,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13678,12 +13720,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13693,7 +13735,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13752,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13725,7 +13767,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -12430,22 +12430,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12455,29 +12455,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12487,29 +12487,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12519,29 +12519,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12551,29 +12551,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12583,29 +12583,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12615,14 +12615,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -12659,17 +12659,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12691,17 +12691,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12723,17 +12723,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12743,29 +12743,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12775,29 +12775,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
@@ -12819,17 +12819,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12851,17 +12851,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12871,29 +12871,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12915,17 +12915,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12979,17 +12979,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12999,29 +12999,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13031,29 +13031,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13075,17 +13075,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13095,29 +13095,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13127,29 +13127,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -13171,17 +13171,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13203,17 +13203,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13223,29 +13223,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13255,29 +13255,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13287,29 +13287,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13319,29 +13319,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13351,29 +13351,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13491,17 +13491,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13518,22 +13518,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13550,22 +13550,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13619,17 +13619,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13646,22 +13646,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13678,22 +13678,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13752,12 +13752,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10416,7 +10416,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
     </row>
@@ -12430,22 +12430,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12472,12 +12472,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12499,17 +12499,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12519,29 +12519,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12563,17 +12563,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12583,29 +12583,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12615,29 +12615,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12659,17 +12659,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12691,17 +12691,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12723,17 +12723,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -12814,22 +12814,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12839,29 +12839,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12871,29 +12871,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12903,29 +12903,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12935,29 +12935,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12967,14 +12967,14 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -13011,17 +13011,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -13043,17 +13043,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13063,29 +13063,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13095,29 +13095,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
@@ -13139,17 +13139,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13159,29 +13159,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13191,29 +13191,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13223,29 +13223,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13255,29 +13255,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13287,29 +13287,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13319,29 +13319,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13351,29 +13351,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -13454,22 +13454,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13491,17 +13491,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13523,17 +13523,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13555,17 +13555,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13614,22 +13614,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13646,22 +13646,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13678,22 +13678,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13752,12 +13752,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（49家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,14 +665,14 @@
         <v>883</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -875,10 +875,10 @@
         <v>8793</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8776</v>
+        <v>8777</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -4547,24 +4547,24 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>-1</v>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>0</v>
@@ -4680,14 +4680,14 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>0</v>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>0</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>0</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>0</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>0</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -4848,14 +4848,14 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>0</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>0</v>
@@ -10101,7 +10101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10109,6 +10109,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10137,6 +10138,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10164,6 +10170,11 @@
           <t>广东省广州市白云区广从一路162号枫兴汽车城内</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10191,6 +10202,11 @@
           <t>黑龙江省大庆高新区庆新大街7号</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10218,6 +10234,11 @@
           <t>江苏省苏州市太仓市北京西路 8 号地块 1#楼</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10245,6 +10266,11 @@
           <t>贵州省黔东南苗族侗族自治州凯里市白午街道凯里经济开发区金源东大道28号经纬国际汽车城3号地块29幢-2层1号</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10272,6 +10298,11 @@
           <t>上海市金山区龙皓路1088号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10299,6 +10330,11 @@
           <t>广东省江门市台山市台城街道舜德路133号</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10326,6 +10362,11 @@
           <t>江苏省无锡市锡山区艳阳路2号</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -10353,6 +10394,11 @@
           <t>重庆市涪陵区宝龙广场LG层中庭</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -10380,6 +10426,11 @@
           <t>抚州市临川区迎宾大道赣东国际汽车城1888号</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -10407,6 +10458,11 @@
           <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -10416,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10431,7 +10487,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10458,7 +10519,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10485,7 +10551,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10515,6 +10586,11 @@
           <t>内蒙古自治区赤峰市红山区桥北物流园区商务广场南侧赤锡路107号</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10542,6 +10618,11 @@
           <t>广东省深圳市光明区观光路与光明大道交叉口蓝鲸世界 L1层L1-07/08号铺位</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10569,6 +10650,11 @@
           <t>西藏自治区拉萨市城关区纳金东路与红旗东路交叉口东南480米YX-HD-ZT-002</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10596,6 +10682,11 @@
           <t>北京市石景山区古城大街(特钢公司厂内）北京国际汽车贸易服务园区F20号</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10623,6 +10714,11 @@
           <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10650,6 +10746,11 @@
           <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10677,6 +10778,11 @@
           <t>四川省成都市高新区火车南站西路2080号</t>
         </is>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10686,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10702,6 +10808,11 @@
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10731,6 +10842,11 @@
           <t>山西省大同市平城区永泰南路星茂汇一层华为</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10758,6 +10874,11 @@
           <t>广西壮族自治区南宁市江南区金凯路8号龙光蓝鲸世界L1层L1-48-49-50A商铺</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10785,6 +10906,11 @@
           <t>江苏省无锡市锡山区安镇街道先锋中路25-4号</t>
         </is>
       </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10812,6 +10938,11 @@
           <t>江苏省苏州市吴江区万象汇1F华为授权体验店</t>
         </is>
       </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10839,6 +10970,11 @@
           <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -10866,6 +11002,11 @@
           <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -10893,6 +11034,11 @@
           <t>河南省郑州市嵩山南路与柳江路交叉口嵩南印象城L1-05</t>
         </is>
       </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -10920,6 +11066,11 @@
           <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼1层03号</t>
         </is>
       </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -10947,6 +11098,11 @@
           <t>湖南省永州市零陵区永州大道接履桥镇晓深塘村（潇湘汽车城内）</t>
         </is>
       </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -10974,6 +11130,11 @@
           <t>贵州省贵阳市观山湖区兴筑路华润万象汇LG层139号</t>
         </is>
       </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -10999,6 +11160,11 @@
       <c r="E33" s="4" t="inlineStr">
         <is>
           <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11013,14 +11179,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11049,6 +11216,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -11076,6 +11248,11 @@
           <t>广东省东莞市东城街道莞龙路（辅道）柏洲边段200号</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11103,6 +11280,11 @@
           <t>广东省湛江市赤坎区东盛路7号S16海田国际汽车城内</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -11130,6 +11312,11 @@
           <t>江苏省无锡市江阴市芙蓉大道436号（周庄段，东风大道路口）</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11157,6 +11344,11 @@
           <t>河北省保定市清苑区振清南街806号</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -11184,6 +11376,11 @@
           <t>河南省郑州市二七区京广路街道京广南路101号</t>
         </is>
       </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -11211,6 +11408,11 @@
           <t>湖南省长沙市岳麓区麓谷汽车世界嘉运路36号</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -11238,6 +11440,11 @@
           <t>贵州省毕节市双山新区碧阳大道佰润汽车公园</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11265,6 +11472,11 @@
           <t>辽宁省丹东市振兴区集环南路1号</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -11292,6 +11504,11 @@
           <t>上海市浦东新区鸿音路2555号临港万达YX-HD-ZT-101</t>
         </is>
       </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -11301,7 +11518,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11316,7 +11533,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11550,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11343,7 +11565,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11373,6 +11600,11 @@
           <t>山东省寿光市圣城街道学院路1111号万达广场1楼中庭</t>
         </is>
       </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -11382,7 +11614,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11397,7 +11629,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11646,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11424,7 +11661,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11454,6 +11696,11 @@
           <t>东莞松山湖万象汇1层中庭</t>
         </is>
       </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -11481,6 +11728,11 @@
           <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -11508,6 +11760,11 @@
           <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -11535,6 +11792,11 @@
           <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -11562,6 +11824,11 @@
           <t>东丰1路3号百利广场1楼中庭</t>
         </is>
       </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -11589,6 +11856,11 @@
           <t>中山北路1号金地商都西门入口南侧</t>
         </is>
       </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -11616,6 +11888,11 @@
           <t>江西省萍乡市安源区萍安北大道天虹购物中心1F</t>
         </is>
       </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -11643,6 +11920,11 @@
           <t>浙江省嘉兴市平湖市南市路811号平湖吾悦1019与1040中间</t>
         </is>
       </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -11652,7 +11934,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11667,7 +11949,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11966,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11694,7 +11981,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11998,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11721,7 +12013,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11751,6 +12048,11 @@
           <t>双塔路置诚广场中庭</t>
         </is>
       </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -11778,31 +12080,41 @@
           <t>湖北省荆州市沙市区江汉北路109号1F中庭</t>
         </is>
       </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>小米之家湖南省长沙市岳麓区长沙万象城汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>桐兴巷与铜盆湖路交叉口西北160米</t>
+          <t>青岛市市北区四流南路22号-8幢展厅</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11814,22 +12126,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾广物汽车城销售服务中心</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>汕尾市</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅</t>
+          <t>汕尾市城区红草镇海汕公路西侧工业园区（三和村与拾和村之间）</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11841,22 +12158,27 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾广物汽车城销售服务中心</t>
+          <t>小鹏汽车南京华采天地销售中心</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>汕尾市</t>
+          <t>南京市</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>汕尾市城区红草镇海汕公路西侧工业园区（三和村与拾和村之间）</t>
+          <t>南京市建邺区江东中路258号 南京华采天地购物中心【F1-17】铺</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11868,7 +12190,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车南京华采天地销售中心</t>
+          <t>小鹏汽车无锡圆融广场销售中心</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -11878,39 +12200,49 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>南京市建邺区江东中路258号 南京华采天地购物中心【F1-17】铺</t>
+          <t>江苏省无锡市梁溪区锡澄路与江海路交叉口圆融广场1楼1300-1310</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡圆融广场销售中心</t>
+          <t>北京昌平悦荟城市中心店</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>江苏省无锡市梁溪区锡澄路与江海路交叉口圆融广场1楼1300-1310</t>
+          <t>北京市昌平区南环中路10号院1号楼1层L1023+L1024</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11922,22 +12254,27 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>北京昌平悦荟城市中心店</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>北京市昌平区南环中路10号院1号楼1层L1023+L1024</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -11949,7 +12286,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11964,34 +12301,44 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>上海世博天地</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>上海市浦东新区世博大道1467号世博天地L1-A</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12003,49 +12350,59 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>上海世博天地</t>
+          <t>盐城永宁</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>盐城市</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>上海市浦东新区世博大道1467号世博天地L1-A</t>
+          <t>江苏省盐城市盐都区厚德路99号</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>盐城永宁</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>盐城市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区厚德路99号</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12075,6 +12432,11 @@
           <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -12084,22 +12446,27 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 绵阳涪城万达广场</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>绵阳市</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>四川省绵阳市涪城区朝阳街道花园路9号</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12111,49 +12478,59 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 绵阳涪城万达广场</t>
+          <t>蔚来空间 | 太仓华发广场</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>绵阳市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>四川省绵阳市涪城区朝阳街道花园路9号</t>
+          <t>南郊太平新路8号1楼106a号店铺</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 太仓华发广场</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>南郊太平新路8号1楼106a号店铺</t>
+          <t>山东省济南市历城区唐冶中路5199号银座·新辰天地L1层005号铺</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12542,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12175,12 +12552,17 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5199号银座·新辰天地L1层005号铺</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12192,22 +12574,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12219,22 +12606,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•金华金东万达</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>金华市</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12246,22 +12638,27 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•金华金东万达</t>
+          <t>华为智能生活馆•恩施和润城</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>金华市</t>
+          <t>恩施土家族苗族自治州</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
+          <t>恩施土家族苗族自治州恩施市施州大道168号</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12273,22 +12670,27 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•恩施和润城</t>
+          <t>华为智能生活馆•榆林万达广场</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>恩施土家族苗族自治州</t>
+          <t>榆林市</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>恩施土家族苗族自治州恩施市施州大道168号</t>
+          <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12702,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•榆林万达广场</t>
+          <t>华为授权体验店（南门王府井）</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12310,12 +12712,17 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>榆林市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
+          <t>陕西省西安市碑林区王府井永宁门店南馆一、二层1A01号</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12327,49 +12734,27 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南门王府井）</t>
+          <t>鸿蒙智行尚界用户中心•牡丹江兴业路</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>牡丹江市</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市碑林区王府井永宁门店南馆一、二层1A01号</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•牡丹江兴业路</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>牡丹江市</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
           <t>黑龙江省牡丹江市阳明区兴业路78号</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12430,22 +12815,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12455,29 +12840,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12487,29 +12872,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12519,29 +12904,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12551,29 +12936,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12583,29 +12968,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12615,7 +13000,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -12627,17 +13012,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12647,29 +13032,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12679,29 +13064,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12711,29 +13096,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12743,7 +13128,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12755,17 +13140,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12775,29 +13160,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12807,29 +13192,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12839,29 +13224,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12871,29 +13256,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12903,7 +13288,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12942,22 +13327,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12967,7 +13352,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12979,17 +13364,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12999,29 +13384,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13031,7 +13416,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13043,17 +13428,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13063,29 +13448,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13095,29 +13480,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13127,29 +13512,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13159,29 +13544,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13191,7 +13576,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13203,17 +13588,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13223,29 +13608,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13255,7 +13640,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13267,17 +13652,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13287,29 +13672,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13319,29 +13704,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13351,29 +13736,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13383,7 +13768,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -13395,17 +13780,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13415,7 +13800,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13427,17 +13812,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13447,7 +13832,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13459,17 +13844,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13486,22 +13871,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13518,22 +13903,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13555,17 +13940,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13592,12 +13977,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13619,17 +14004,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13651,17 +14036,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13683,17 +14068,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -11187,7 +11187,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「东营市奥润汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「江苏天奥汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「湖南华洋华迪汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「辽阳惠华新业汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期存在高相似店名「小鹏汽车青岛青锋国际汽车城销售服务中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「华为授权体验店（融创广场）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「华为授权体验店（王府井）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13352,29 +13352,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•北京丰管路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13384,29 +13384,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13512,14 +13512,14 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13556,17 +13556,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13576,29 +13576,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13608,29 +13608,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
         </is>
       </c>
     </row>
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -13684,17 +13684,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13716,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
         </is>
       </c>
     </row>
@@ -13839,22 +13839,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13871,22 +13871,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13903,22 +13903,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13967,7 +13967,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -13977,12 +13977,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14004,17 +14004,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14031,22 +14031,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14063,22 +14063,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（42条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1733</v>
+        <v>1471</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1741</v>
+        <v>1473</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8793</v>
+        <v>8531</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8777</v>
+        <v>8509</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="C407" s="3" t="n">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="E407" s="3" t="n">
         <v>-2</v>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E408" s="3" t="n">
         <v>-2</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>206</v>
+        <v>143</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>205</v>
+        <v>142</v>
       </c>
       <c r="E409" s="3" t="n">
         <v>-1</v>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E410" s="3" t="n">
         <v>-1</v>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>-1</v>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,80 +9846,80 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C426" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D426" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E426" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B427" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C427" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="D427" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="E427" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B428" s="4" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C428" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D428" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="E428" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B429" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C429" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D429" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="E429" s="4" t="n">
-        <v>1</v>
+      <c r="C429" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,17 +10014,17 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E434" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C435" s="4" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E435" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C436" s="4" t="n">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -10081,10 +10081,10 @@
         </is>
       </c>
       <c r="C437" s="4" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D437" s="4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E437" s="4" t="n">
         <v>2</v>
@@ -10101,7 +10101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10109,7 +10109,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10664,27 +10664,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京首钢园</t>
+          <t>AITO授权用户中心•长春华阳</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>长春市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>北京市石景山区古城大街(特钢公司厂内）北京国际汽车贸易服务园区F20号</t>
+          <t>吉林省长春市经开区东南湖大路1011号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10696,27 +10696,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•大同星茂汇</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>山西省大同市平城区永泰南路星茂汇一层华为</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10728,22 +10728,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•长春华阳</t>
+          <t>华为智能生活馆•南宁龙光蓝鲸世界</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市经开区东南湖大路1011号</t>
+          <t>广西壮族自治区南宁市江南区金凯路8号龙光蓝鲸世界L1层L1-48-49-50A商铺</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10760,22 +10760,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•成都机场路</t>
+          <t>华为授权体验店（吴江万象汇）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市高新区火车南站西路2080号</t>
+          <t>江苏省苏州市吴江区万象汇1F华为授权体验店</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10792,27 +10792,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>石家庄市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•大同星茂汇</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>石家庄市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山西省大同市平城区永泰南路星茂汇一层华为</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10856,22 +10856,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•南宁龙光蓝鲸世界</t>
+          <t>华为授权体验店（嵩南印象城）</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市江南区金凯路8号龙光蓝鲸世界L1层L1-48-49-50A商铺</t>
+          <t>河南省郑州市嵩山南路与柳江路交叉口嵩南印象城L1-05</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10888,22 +10888,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•无锡先锋中路</t>
+          <t>华为智能生活馆•贵阳万象汇</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区安镇街道先锋中路25-4号</t>
+          <t>贵州省贵阳市观山湖区兴筑路华润万象汇LG层139号</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -10920,249 +10920,25 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（吴江万象汇）</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区万象汇1F华为授权体验店</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>石家庄市</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>华为授权体验店（桥西勒泰）</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>石家庄市</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>华为授权体验店（嵩南印象城）</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>郑州市</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>河南省郑州市嵩山南路与柳江路交叉口嵩南印象城L1-05</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•杭州梦马汽车小镇</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼1层03号</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•永州潇湘汽车城</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>永州市</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>湖南省永州市零陵区永州大道接履桥镇晓深塘村（潇湘汽车城内）</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•贵阳万象汇</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>贵州省贵阳市观山湖区兴筑路华润万象汇LG层139号</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>华为授权体验店（悦荟）</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>全新</t>
         </is>
@@ -11179,7 +10955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11934,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11949,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11966,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11981,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11998,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -12013,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12254,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12269,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12286,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12301,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12382,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12397,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12414,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12429,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12574,27 +12350,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•金华金东万达</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>金华市</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>广东省肇庆市端州区迎宾大道肇庆学院东侧</t>
+          <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12606,22 +12382,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•金华金东万达</t>
+          <t>华为智能生活馆•恩施和润城</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>金华市</t>
+          <t>恩施土家族苗族自治州</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
+          <t>恩施土家族苗族自治州恩施市施州大道168号</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -12638,22 +12414,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•恩施和润城</t>
+          <t>华为智能生活馆•榆林万达广场</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>恩施土家族苗族自治州</t>
+          <t>榆林市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>恩施土家族苗族自治州恩施市施州大道168号</t>
+          <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -12670,7 +12446,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•榆林万达广场</t>
+          <t>华为授权体验店（南门王府井）</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12680,17 +12456,17 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>榆林市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
+          <t>陕西省西安市碑林区王府井永宁门店南馆一、二层1A01号</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 4 期；本期存在高相似店名「华为授权体验店（王府井）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12702,57 +12478,25 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南门王府井）</t>
+          <t>鸿蒙智行尚界用户中心•牡丹江兴业路</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>牡丹江市</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>陕西省西安市碑林区王府井永宁门店南馆一、二层1A01号</t>
+          <t>黑龙江省牡丹江市阳明区兴业路78号</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 4 期；本期存在高相似店名「华为授权体验店（王府井）」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•牡丹江兴业路</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>牡丹江市</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>黑龙江省牡丹江市阳明区兴业路78号</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>连续在档 4 期</t>
         </is>
@@ -12769,7 +12513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12815,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12840,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12904,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12936,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12968,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13000,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州凯马汽车城</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13032,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路152号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•重庆北滨一路</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13064,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区北滨一路210号 → 重庆市两江新区北滨一路210号附1-4号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13096,14 +12840,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -13113,12 +12857,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13128,29 +12872,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米 → 河北省衡水市高新技术开发区胜利西路2088号1幢103号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海沪松公路</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13160,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区沪松公路1217号 → 上海市松江区九亭镇沪松公路1217号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -13172,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13192,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13209,12 +12953,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13224,29 +12968,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13256,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13288,29 +13032,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13320,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13352,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京丰管路</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13384,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市丰台区丰管路46号 → 北京市丰台区丰管路46号西南三环丰益桥西900米路南</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•郑州梧桐街汽车园</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13416,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>郑州市梧桐街与须水河西路交叉口向西201米路南 → 河南省郑州市高新技术产业开发区梧桐街与须水河西路西300米路南8号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13448,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13480,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13236,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13512,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -13524,27 +13268,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13556,49 +13300,49 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13608,29 +13352,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13640,29 +13384,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号（临时营业） → 重庆市涪陵区迎宾大道50号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13672,29 +13416,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13704,29 +13448,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13736,29 +13480,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>陕西省汉中市汉台区七里街道办事处兴汉路北侧博望路东侧整栋(车管所向东200米) → 陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13768,391 +13512,39 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（K11）</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•眉山眉州大道</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（万象汇）</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•遂宁物流港汽车城</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•遂宁物流港汽车城</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
           <t>地址相似度 75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8531</v>
+        <v>8530</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8509</v>
+        <v>8508</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-22</v>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -12591,22 +12591,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,14 +13000,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13017,12 +13017,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13199,22 +13199,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -13327,22 +13327,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12953,12 +12953,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,14 +13000,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13017,12 +13017,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,14 +12808,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12911,22 +12911,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13231,22 +13231,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12975,22 +12975,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（25家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13145,12 +13145,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13327,22 +13327,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -12889,12 +12889,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12985,12 +12985,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13327,22 +13327,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
